--- a/miomio/后台升级表格/到达国仓/DPN货物入库.xlsx
+++ b/miomio/后台升级表格/到达国仓/DPN货物入库.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12420"/>
+    <workbookView windowHeight="18320"/>
   </bookViews>
   <sheets>
     <sheet name="列表" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,20 @@
     <sheet name="点击订单号或更多" sheetId="6" r:id="rId3"/>
     <sheet name="货物入库" sheetId="11" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1030,14 +1043,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="43">
     <font>
@@ -1101,6 +1114,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1119,12 +1138,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1171,34 +1184,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -1212,14 +1197,6 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1259,6 +1236,21 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1309,7 +1301,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1322,6 +1335,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF0070C0"/>
       <name val="Microsoft JhengHei"/>
@@ -1331,12 +1350,6 @@
       <sz val="8"/>
       <color rgb="FF0070C0"/>
       <name val="Microsoft JhengHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1391,55 +1404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1457,25 +1428,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1499,6 +1464,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1511,7 +1482,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1535,7 +1530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1554,6 +1561,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1599,10 +1612,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1625,26 +1658,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1684,21 +1697,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -1727,6 +1725,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1785,152 +1798,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1955,7 +1968,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1964,19 +1980,25 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1985,97 +2007,85 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2108,6 +2118,9 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2126,6 +2139,9 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2141,7 +2157,10 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2150,10 +2169,34 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2162,66 +2205,24 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2231,16 +2232,16 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2248,6 +2249,15 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2255,52 +2265,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -2611,89 +2621,89 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="51" customWidth="1"/>
-    <col min="2" max="2" width="15.625" style="52" customWidth="1"/>
-    <col min="3" max="3" width="20.625" style="51" customWidth="1"/>
-    <col min="4" max="12" width="15.625" style="51" customWidth="1"/>
-    <col min="13" max="13" width="15.625" style="52" customWidth="1"/>
-    <col min="14" max="14" width="15.625" style="51" customWidth="1"/>
-    <col min="15" max="15" width="18.25" style="51" customWidth="1"/>
-    <col min="17" max="18" width="15.625" style="51" customWidth="1"/>
-    <col min="19" max="19" width="13.625" style="51" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="51"/>
+    <col min="1" max="1" width="5.625" style="50" customWidth="1"/>
+    <col min="2" max="2" width="15.625" style="51" customWidth="1"/>
+    <col min="3" max="3" width="20.625" style="50" customWidth="1"/>
+    <col min="4" max="12" width="15.625" style="50" customWidth="1"/>
+    <col min="13" max="13" width="15.625" style="51" customWidth="1"/>
+    <col min="14" max="14" width="15.625" style="50" customWidth="1"/>
+    <col min="15" max="15" width="18.25" style="50" customWidth="1"/>
+    <col min="17" max="18" width="15.625" style="50" customWidth="1"/>
+    <col min="19" max="19" width="13.625" style="50" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" s="49" customFormat="1" ht="30" customHeight="1" spans="1:15">
-      <c r="A1" s="53" t="s">
+    <row r="1" s="48" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="55" t="s">
+      <c r="B1" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="57"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="57"/>
-      <c r="O1" s="57"/>
-    </row>
-    <row r="2" s="49" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="F1" s="56"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="56"/>
+      <c r="O1" s="56"/>
+    </row>
+    <row r="2" s="48" customFormat="1" ht="30" customHeight="1" spans="1:15">
       <c r="A2" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="57"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="57"/>
-      <c r="O2" s="57"/>
-    </row>
-    <row r="3" s="49" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="56"/>
+      <c r="O2" s="56"/>
+    </row>
+    <row r="3" s="48" customFormat="1" ht="30" customHeight="1" spans="1:15">
       <c r="A3" s="61"/>
       <c r="B3" s="62"/>
       <c r="C3" s="61"/>
       <c r="D3" s="61"/>
       <c r="E3" s="61"/>
       <c r="F3" s="61"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="57"/>
-      <c r="O3" s="57"/>
-    </row>
-    <row r="4" s="49" customFormat="1" ht="30" customHeight="1" spans="1:13">
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="56"/>
+      <c r="O3" s="56"/>
+    </row>
+    <row r="4" s="48" customFormat="1" ht="30" customHeight="1" spans="1:15">
       <c r="A4" s="63" t="s">
         <v>0</v>
       </c>
@@ -2724,7 +2734,7 @@
       <c r="J4" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="84" t="s">
+      <c r="K4" s="65" t="s">
         <v>18</v>
       </c>
       <c r="L4" s="63" t="s">
@@ -2734,7 +2744,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" s="49" customFormat="1" ht="30" customHeight="1" spans="1:13">
+    <row r="5" s="48" customFormat="1" ht="30" customHeight="1" spans="1:15">
       <c r="A5" s="63" t="s">
         <v>0</v>
       </c>
@@ -2765,7 +2775,7 @@
       <c r="J5" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="84" t="s">
+      <c r="K5" s="65" t="s">
         <v>30</v>
       </c>
       <c r="L5" s="63" t="s">
@@ -2775,940 +2785,940 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" s="50" customFormat="1" ht="30" customHeight="1" spans="1:15">
-      <c r="A6" s="65" t="s">
+    <row r="6" s="49" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A6" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="58" t="s">
+      <c r="B6" s="67"/>
+      <c r="C6" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="58" t="s">
+      <c r="D6" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="58" t="s">
+      <c r="E6" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="58" t="s">
+      <c r="F6" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="58"/>
-      <c r="O6" s="58"/>
-    </row>
-    <row r="7" s="49" customFormat="1" ht="30" customHeight="1" spans="1:15">
-      <c r="A7" s="67" t="s">
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="57"/>
+      <c r="O6" s="57"/>
+    </row>
+    <row r="7" s="48" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A7" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69" t="s">
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="69" t="s">
+      <c r="K7" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="69" t="s">
+      <c r="L7" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="M7" s="68" t="s">
+      <c r="M7" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="69" t="s">
+      <c r="N7" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="O7" s="85" t="s">
+      <c r="O7" s="71" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:15">
-      <c r="A8" s="70">
-        <v>1</v>
-      </c>
-      <c r="B8" s="71" t="s">
+      <c r="A8" s="72">
+        <v>1</v>
+      </c>
+      <c r="B8" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="73" t="s">
+      <c r="E8" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="86">
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="76">
         <v>10</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="77">
         <v>12</v>
       </c>
-      <c r="L8" s="87" t="s">
+      <c r="L8" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="88" t="s">
+      <c r="M8" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="89" t="s">
+      <c r="N8" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="O8" s="90">
+      <c r="O8" s="81">
         <v>43763.4969328704</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:15">
-      <c r="A9" s="70"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="42" t="s">
+      <c r="A9" s="72"/>
+      <c r="B9" s="73"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="73" t="s">
+      <c r="E9" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="86">
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="76">
         <v>20</v>
       </c>
-      <c r="K9" s="79">
+      <c r="K9" s="77">
         <v>13</v>
       </c>
-      <c r="L9" s="91"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="89"/>
-      <c r="O9" s="90"/>
+      <c r="L9" s="82"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="80"/>
+      <c r="O9" s="81"/>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:15">
-      <c r="A10" s="70"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="42" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="73" t="s">
+      <c r="E10" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="86">
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="76">
         <v>20</v>
       </c>
-      <c r="K10" s="79">
+      <c r="K10" s="77">
         <v>14</v>
       </c>
-      <c r="L10" s="91"/>
-      <c r="M10" s="92"/>
-      <c r="N10" s="89"/>
-      <c r="O10" s="90"/>
+      <c r="L10" s="82"/>
+      <c r="M10" s="83"/>
+      <c r="N10" s="80"/>
+      <c r="O10" s="81"/>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:15">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="42" t="s">
+      <c r="A11" s="72"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="73" t="s">
+      <c r="E11" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="86">
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="76">
         <v>35</v>
       </c>
-      <c r="K11" s="79">
+      <c r="K11" s="77">
         <v>15</v>
       </c>
-      <c r="L11" s="91"/>
-      <c r="M11" s="92"/>
-      <c r="N11" s="89"/>
-      <c r="O11" s="90"/>
+      <c r="L11" s="82"/>
+      <c r="M11" s="83"/>
+      <c r="N11" s="80"/>
+      <c r="O11" s="81"/>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:15">
-      <c r="A12" s="74">
+      <c r="A12" s="84">
         <v>2</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="D12" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="76">
-        <v>1</v>
-      </c>
-      <c r="K12" s="76">
-        <v>1</v>
-      </c>
-      <c r="L12" s="93" t="s">
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="86">
+        <v>1</v>
+      </c>
+      <c r="K12" s="86">
+        <v>1</v>
+      </c>
+      <c r="L12" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="M12" s="94" t="s">
+      <c r="M12" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="N12" s="95" t="s">
+      <c r="N12" s="90" t="s">
         <v>62</v>
       </c>
-      <c r="O12" s="96">
+      <c r="O12" s="91">
         <v>43763.4969328704</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:15">
-      <c r="A13" s="70">
+      <c r="A13" s="72">
         <v>3</v>
       </c>
-      <c r="B13" s="78" t="s">
+      <c r="B13" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="42" t="s">
+      <c r="D13" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="73" t="s">
+      <c r="E13" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="79">
-        <v>1</v>
-      </c>
-      <c r="K13" s="79">
-        <v>1</v>
-      </c>
-      <c r="L13" s="97" t="s">
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="77">
+        <v>1</v>
+      </c>
+      <c r="K13" s="77">
+        <v>1</v>
+      </c>
+      <c r="L13" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="M13" s="98" t="s">
+      <c r="M13" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="N13" s="99" t="s">
+      <c r="N13" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="O13" s="90">
+      <c r="O13" s="81">
         <v>43763.4969328704</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:15">
-      <c r="A14" s="74">
+      <c r="A14" s="84">
         <v>4</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="47" t="s">
+      <c r="D14" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="77" t="s">
+      <c r="E14" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="76">
-        <v>1</v>
-      </c>
-      <c r="K14" s="76">
-        <v>1</v>
-      </c>
-      <c r="L14" s="93" t="s">
+      <c r="F14" s="87"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="86">
+        <v>1</v>
+      </c>
+      <c r="K14" s="86">
+        <v>1</v>
+      </c>
+      <c r="L14" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="M14" s="94" t="s">
+      <c r="M14" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="N14" s="95" t="s">
+      <c r="N14" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="O14" s="96">
+      <c r="O14" s="91">
         <v>43764.4969328704</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:15">
-      <c r="A15" s="70">
+      <c r="A15" s="72">
         <v>5</v>
       </c>
-      <c r="B15" s="78" t="s">
+      <c r="B15" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="79" t="s">
+      <c r="C15" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="42" t="s">
+      <c r="D15" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="73" t="s">
+      <c r="E15" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="79">
-        <v>1</v>
-      </c>
-      <c r="K15" s="79">
-        <v>1</v>
-      </c>
-      <c r="L15" s="97" t="s">
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="77">
+        <v>1</v>
+      </c>
+      <c r="K15" s="77">
+        <v>1</v>
+      </c>
+      <c r="L15" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="M15" s="98" t="s">
+      <c r="M15" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="N15" s="99" t="s">
+      <c r="N15" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="O15" s="90">
+      <c r="O15" s="81">
         <v>43765.4969328704</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:15">
-      <c r="A16" s="74">
+      <c r="A16" s="84">
         <v>6</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="77" t="s">
+      <c r="E16" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="76">
-        <v>1</v>
-      </c>
-      <c r="K16" s="76">
-        <v>1</v>
-      </c>
-      <c r="L16" s="100" t="s">
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="86">
+        <v>1</v>
+      </c>
+      <c r="K16" s="86">
+        <v>1</v>
+      </c>
+      <c r="L16" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="M16" s="101" t="s">
+      <c r="M16" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="N16" s="76" t="s">
+      <c r="N16" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="O16" s="96">
+      <c r="O16" s="91">
         <v>43766.4969328704</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:15">
-      <c r="A17" s="70">
+      <c r="A17" s="72">
         <v>7</v>
       </c>
-      <c r="B17" s="78" t="s">
+      <c r="B17" s="92" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="42" t="s">
+      <c r="D17" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="73" t="s">
+      <c r="E17" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="79">
-        <v>1</v>
-      </c>
-      <c r="K17" s="79">
-        <v>1</v>
-      </c>
-      <c r="L17" s="102" t="s">
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="75"/>
+      <c r="J17" s="77">
+        <v>1</v>
+      </c>
+      <c r="K17" s="77">
+        <v>1</v>
+      </c>
+      <c r="L17" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="M17" s="103" t="s">
+      <c r="M17" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="N17" s="79" t="s">
+      <c r="N17" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="O17" s="90">
+      <c r="O17" s="81">
         <v>43767.4969328704</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:15">
-      <c r="A18" s="74">
+      <c r="A18" s="84">
         <v>8</v>
       </c>
-      <c r="B18" s="75" t="s">
+      <c r="B18" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="D18" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="77" t="s">
+      <c r="E18" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="76">
-        <v>1</v>
-      </c>
-      <c r="K18" s="76">
-        <v>1</v>
-      </c>
-      <c r="L18" s="100" t="s">
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="86">
+        <v>1</v>
+      </c>
+      <c r="K18" s="86">
+        <v>1</v>
+      </c>
+      <c r="L18" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="M18" s="101" t="s">
+      <c r="M18" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="N18" s="76" t="s">
+      <c r="N18" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="O18" s="96">
+      <c r="O18" s="91">
         <v>43768.4969328704</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:15">
-      <c r="A19" s="70">
+      <c r="A19" s="72">
         <v>9</v>
       </c>
-      <c r="B19" s="78" t="s">
+      <c r="B19" s="92" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="79" t="s">
+      <c r="C19" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D19" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="73" t="s">
+      <c r="E19" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="79">
-        <v>1</v>
-      </c>
-      <c r="K19" s="79">
-        <v>1</v>
-      </c>
-      <c r="L19" s="102" t="s">
+      <c r="F19" s="75"/>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="75"/>
+      <c r="J19" s="77">
+        <v>1</v>
+      </c>
+      <c r="K19" s="77">
+        <v>1</v>
+      </c>
+      <c r="L19" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="M19" s="103" t="s">
+      <c r="M19" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="N19" s="79" t="s">
+      <c r="N19" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="O19" s="90">
+      <c r="O19" s="81">
         <v>43769.4969328704</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:15">
-      <c r="A20" s="74">
+      <c r="A20" s="84">
         <v>10</v>
       </c>
-      <c r="B20" s="75" t="s">
+      <c r="B20" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="77" t="s">
+      <c r="E20" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="76">
-        <v>1</v>
-      </c>
-      <c r="K20" s="76">
-        <v>1</v>
-      </c>
-      <c r="L20" s="100" t="s">
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="87"/>
+      <c r="J20" s="86">
+        <v>1</v>
+      </c>
+      <c r="K20" s="86">
+        <v>1</v>
+      </c>
+      <c r="L20" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="M20" s="101" t="s">
+      <c r="M20" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="N20" s="76" t="s">
+      <c r="N20" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="O20" s="96">
+      <c r="O20" s="91">
         <v>43770.4969328704</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:15">
-      <c r="A21" s="70">
+      <c r="A21" s="72">
         <v>11</v>
       </c>
-      <c r="B21" s="78" t="s">
+      <c r="B21" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="79" t="s">
+      <c r="C21" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="42" t="s">
+      <c r="D21" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="E21" s="73" t="s">
+      <c r="E21" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="73"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="73"/>
-      <c r="J21" s="79">
-        <v>1</v>
-      </c>
-      <c r="K21" s="79">
-        <v>1</v>
-      </c>
-      <c r="L21" s="102" t="s">
+      <c r="F21" s="75"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="75"/>
+      <c r="J21" s="77">
+        <v>1</v>
+      </c>
+      <c r="K21" s="77">
+        <v>1</v>
+      </c>
+      <c r="L21" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="M21" s="103" t="s">
+      <c r="M21" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="N21" s="79" t="s">
+      <c r="N21" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="O21" s="90">
+      <c r="O21" s="81">
         <v>43771.4969328704</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:15">
-      <c r="A22" s="74">
+      <c r="A22" s="84">
         <v>12</v>
       </c>
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="47" t="s">
+      <c r="D22" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="77" t="s">
+      <c r="E22" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="76">
-        <v>1</v>
-      </c>
-      <c r="K22" s="76">
-        <v>1</v>
-      </c>
-      <c r="L22" s="100" t="s">
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="87"/>
+      <c r="I22" s="87"/>
+      <c r="J22" s="86">
+        <v>1</v>
+      </c>
+      <c r="K22" s="86">
+        <v>1</v>
+      </c>
+      <c r="L22" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="M22" s="101" t="s">
+      <c r="M22" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="N22" s="76" t="s">
+      <c r="N22" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="O22" s="96">
+      <c r="O22" s="91">
         <v>43772.4969328704</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:15">
-      <c r="A23" s="70">
+      <c r="A23" s="72">
         <v>13</v>
       </c>
-      <c r="B23" s="78" t="s">
+      <c r="B23" s="92" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="79" t="s">
+      <c r="C23" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="73" t="s">
+      <c r="E23" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="79">
-        <v>1</v>
-      </c>
-      <c r="K23" s="79">
-        <v>1</v>
-      </c>
-      <c r="L23" s="102" t="s">
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="77">
+        <v>1</v>
+      </c>
+      <c r="K23" s="77">
+        <v>1</v>
+      </c>
+      <c r="L23" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="M23" s="103" t="s">
+      <c r="M23" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="N23" s="79" t="s">
+      <c r="N23" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="O23" s="90">
+      <c r="O23" s="81">
         <v>43773.4969328704</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:15">
-      <c r="A24" s="74">
+      <c r="A24" s="84">
         <v>14</v>
       </c>
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="76" t="s">
+      <c r="C24" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="47" t="s">
+      <c r="D24" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="77" t="s">
+      <c r="E24" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="76">
-        <v>1</v>
-      </c>
-      <c r="K24" s="76">
-        <v>1</v>
-      </c>
-      <c r="L24" s="104" t="s">
+      <c r="F24" s="87"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="86">
+        <v>1</v>
+      </c>
+      <c r="K24" s="86">
+        <v>1</v>
+      </c>
+      <c r="L24" s="100" t="s">
         <v>89</v>
       </c>
-      <c r="M24" s="101" t="s">
+      <c r="M24" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="N24" s="76" t="s">
+      <c r="N24" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="O24" s="96">
+      <c r="O24" s="91">
         <v>43774.4969328704</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:15">
-      <c r="A25" s="70">
+      <c r="A25" s="72">
         <v>15</v>
       </c>
-      <c r="B25" s="78" t="s">
+      <c r="B25" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="79" t="s">
+      <c r="C25" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="42" t="s">
+      <c r="D25" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="73" t="s">
+      <c r="E25" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="79">
-        <v>1</v>
-      </c>
-      <c r="K25" s="79">
-        <v>1</v>
-      </c>
-      <c r="L25" s="105" t="s">
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="77">
+        <v>1</v>
+      </c>
+      <c r="K25" s="77">
+        <v>1</v>
+      </c>
+      <c r="L25" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="M25" s="103" t="s">
+      <c r="M25" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="N25" s="79" t="s">
+      <c r="N25" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="O25" s="90">
+      <c r="O25" s="81">
         <v>43775.4969328704</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:15">
-      <c r="A26" s="74">
+      <c r="A26" s="84">
         <v>16</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="47" t="s">
+      <c r="D26" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="77" t="s">
+      <c r="E26" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="F26" s="77"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="76">
-        <v>1</v>
-      </c>
-      <c r="K26" s="76">
-        <v>1</v>
-      </c>
-      <c r="L26" s="100" t="s">
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="86">
+        <v>1</v>
+      </c>
+      <c r="K26" s="86">
+        <v>1</v>
+      </c>
+      <c r="L26" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="M26" s="101" t="s">
+      <c r="M26" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="N26" s="76" t="s">
+      <c r="N26" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="O26" s="96">
+      <c r="O26" s="91">
         <v>43776.4969328704</v>
       </c>
     </row>
     <row r="27" ht="35" customHeight="1" spans="1:15">
-      <c r="A27" s="70">
+      <c r="A27" s="72">
         <v>17</v>
       </c>
-      <c r="B27" s="78" t="s">
+      <c r="B27" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="79" t="s">
+      <c r="C27" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="73" t="s">
+      <c r="E27" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="79">
-        <v>1</v>
-      </c>
-      <c r="K27" s="79">
-        <v>1</v>
-      </c>
-      <c r="L27" s="102" t="s">
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="77">
+        <v>1</v>
+      </c>
+      <c r="K27" s="77">
+        <v>1</v>
+      </c>
+      <c r="L27" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="M27" s="103" t="s">
+      <c r="M27" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="N27" s="79" t="s">
+      <c r="N27" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="O27" s="90">
+      <c r="O27" s="81">
         <v>43777.4969328704</v>
       </c>
     </row>
     <row r="28" ht="35" customHeight="1" spans="1:15">
-      <c r="A28" s="74">
+      <c r="A28" s="84">
         <v>18</v>
       </c>
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="76" t="s">
+      <c r="C28" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="47" t="s">
+      <c r="D28" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="E28" s="77" t="s">
+      <c r="E28" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="76">
-        <v>1</v>
-      </c>
-      <c r="K28" s="76">
-        <v>1</v>
-      </c>
-      <c r="L28" s="100" t="s">
+      <c r="F28" s="87"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="87"/>
+      <c r="J28" s="86">
+        <v>1</v>
+      </c>
+      <c r="K28" s="86">
+        <v>1</v>
+      </c>
+      <c r="L28" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="M28" s="101" t="s">
+      <c r="M28" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="N28" s="76" t="s">
+      <c r="N28" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="O28" s="96">
+      <c r="O28" s="91">
         <v>43778.4969328704</v>
       </c>
     </row>
     <row r="29" ht="35" customHeight="1" spans="1:15">
-      <c r="A29" s="70">
+      <c r="A29" s="72">
         <v>19</v>
       </c>
-      <c r="B29" s="78" t="s">
+      <c r="B29" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="C29" s="79" t="s">
+      <c r="C29" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="42" t="s">
+      <c r="D29" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="E29" s="73" t="s">
+      <c r="E29" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="79">
-        <v>1</v>
-      </c>
-      <c r="K29" s="79">
-        <v>1</v>
-      </c>
-      <c r="L29" s="102" t="s">
+      <c r="F29" s="75"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="75"/>
+      <c r="J29" s="77">
+        <v>1</v>
+      </c>
+      <c r="K29" s="77">
+        <v>1</v>
+      </c>
+      <c r="L29" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="M29" s="103" t="s">
+      <c r="M29" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="N29" s="79" t="s">
+      <c r="N29" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="O29" s="90">
+      <c r="O29" s="81">
         <v>43779.4969328704</v>
       </c>
     </row>
     <row r="30" ht="35" customHeight="1" spans="1:15">
-      <c r="A30" s="74">
+      <c r="A30" s="84">
         <v>20</v>
       </c>
-      <c r="B30" s="75" t="s">
+      <c r="B30" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="76" t="s">
+      <c r="C30" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="47" t="s">
+      <c r="D30" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="E30" s="77" t="s">
+      <c r="E30" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="77"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="77"/>
-      <c r="J30" s="76">
-        <v>1</v>
-      </c>
-      <c r="K30" s="76">
-        <v>1</v>
-      </c>
-      <c r="L30" s="100" t="s">
+      <c r="F30" s="87"/>
+      <c r="G30" s="87"/>
+      <c r="H30" s="87"/>
+      <c r="I30" s="87"/>
+      <c r="J30" s="86">
+        <v>1</v>
+      </c>
+      <c r="K30" s="86">
+        <v>1</v>
+      </c>
+      <c r="L30" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="M30" s="101" t="s">
+      <c r="M30" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="N30" s="76" t="s">
+      <c r="N30" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="O30" s="96">
+      <c r="O30" s="91">
         <v>43780.4969328704</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:15">
-      <c r="A31" s="80"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="82"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="82"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="82"/>
-      <c r="H31" s="82"/>
-      <c r="I31" s="82"/>
-      <c r="J31" s="82"/>
-      <c r="K31" s="82"/>
-      <c r="L31" s="82"/>
-      <c r="M31" s="81"/>
-      <c r="N31" s="82"/>
-      <c r="O31" s="106"/>
+      <c r="A31" s="102"/>
+      <c r="B31" s="103"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="103"/>
+      <c r="N31" s="104"/>
+      <c r="O31" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="33">
@@ -3757,7 +3767,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B3:L19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="20.625" style="4" customWidth="1"/>
@@ -3782,485 +3792,485 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="29"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="30" customHeight="1" spans="2:12">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="L4" s="31" t="s">
+      <c r="L4" s="15" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="2:12">
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="16">
-        <v>1</v>
-      </c>
-      <c r="I5" s="42" t="s">
+      <c r="H5" s="19">
+        <v>1</v>
+      </c>
+      <c r="I5" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="19">
         <v>0.52</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="19">
         <v>0.52</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="40">
         <v>0.52</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="2:12">
-      <c r="B6" s="46"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="15" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H6" s="16">
-        <v>1</v>
-      </c>
-      <c r="I6" s="42" t="s">
+      <c r="H6" s="19">
+        <v>1</v>
+      </c>
+      <c r="I6" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="19">
         <v>0.92</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="19">
         <v>0.92</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="40">
         <v>0.92</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="2:12">
-      <c r="B7" s="46"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="15" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H7" s="16">
-        <v>1</v>
-      </c>
-      <c r="I7" s="42" t="s">
+      <c r="H7" s="19">
+        <v>1</v>
+      </c>
+      <c r="I7" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="19">
         <v>0.12</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="19">
         <v>0.12</v>
       </c>
-      <c r="L7" s="43">
+      <c r="L7" s="40">
         <v>0.12</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="2:12">
-      <c r="B8" s="46"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="15" t="s">
+      <c r="B8" s="38"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="16">
-        <v>1</v>
-      </c>
-      <c r="I8" s="42" t="s">
+      <c r="H8" s="19">
+        <v>1</v>
+      </c>
+      <c r="I8" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="19">
         <v>2.2</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="19">
         <v>2.2</v>
       </c>
-      <c r="L8" s="43">
+      <c r="L8" s="40">
         <v>2.2</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="2:12">
-      <c r="B9" s="46"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="15" t="s">
+      <c r="B9" s="38"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H9" s="16">
-        <v>1</v>
-      </c>
-      <c r="I9" s="42" t="s">
+      <c r="H9" s="19">
+        <v>1</v>
+      </c>
+      <c r="I9" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="19">
         <v>7.1</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="19">
         <v>7.1</v>
       </c>
-      <c r="L9" s="43">
+      <c r="L9" s="40">
         <v>7.1</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="2:12">
-      <c r="B10" s="46"/>
-      <c r="C10" s="19" t="s">
+      <c r="B10" s="38"/>
+      <c r="C10" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="19">
-        <v>1</v>
-      </c>
-      <c r="I10" s="47" t="s">
+      <c r="H10" s="24">
+        <v>1</v>
+      </c>
+      <c r="I10" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="24">
         <v>1.14</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="24">
         <v>1.14</v>
       </c>
-      <c r="L10" s="48">
+      <c r="L10" s="47">
         <v>1.14</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="2:12">
-      <c r="B11" s="46"/>
-      <c r="C11" s="16" t="s">
+      <c r="B11" s="38"/>
+      <c r="C11" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="G11" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="16">
-        <v>1</v>
-      </c>
-      <c r="I11" s="42" t="s">
+      <c r="H11" s="19">
+        <v>1</v>
+      </c>
+      <c r="I11" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="19">
         <v>0.92</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="19">
         <v>0.92</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="40">
         <v>0.92</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="2:12">
-      <c r="B12" s="46"/>
-      <c r="C12" s="19" t="s">
+      <c r="B12" s="38"/>
+      <c r="C12" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="H12" s="19">
-        <v>1</v>
-      </c>
-      <c r="I12" s="47" t="s">
+      <c r="H12" s="24">
+        <v>1</v>
+      </c>
+      <c r="I12" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="24">
         <v>0.12</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="24">
         <v>0.12</v>
       </c>
-      <c r="L12" s="48">
+      <c r="L12" s="47">
         <v>0.12</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="2:12">
-      <c r="B13" s="46"/>
-      <c r="C13" s="16" t="s">
+      <c r="B13" s="38"/>
+      <c r="C13" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H13" s="16">
-        <v>1</v>
-      </c>
-      <c r="I13" s="42" t="s">
+      <c r="H13" s="19">
+        <v>1</v>
+      </c>
+      <c r="I13" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="19">
         <v>2.2</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="19">
         <v>2.2</v>
       </c>
-      <c r="L13" s="43">
+      <c r="L13" s="40">
         <v>2.2</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="2:12">
-      <c r="B14" s="46"/>
-      <c r="C14" s="19" t="s">
+      <c r="B14" s="38"/>
+      <c r="C14" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="19">
-        <v>1</v>
-      </c>
-      <c r="I14" s="47" t="s">
+      <c r="H14" s="24">
+        <v>1</v>
+      </c>
+      <c r="I14" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="24">
         <v>7.1</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="24">
         <v>7.1</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="47">
         <v>7.1</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="2:12">
-      <c r="B15" s="46"/>
-      <c r="C15" s="16" t="s">
+      <c r="B15" s="38"/>
+      <c r="C15" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="16">
-        <v>1</v>
-      </c>
-      <c r="I15" s="42" t="s">
+      <c r="H15" s="19">
+        <v>1</v>
+      </c>
+      <c r="I15" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="19">
         <v>1.1</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="19">
         <v>1.1</v>
       </c>
-      <c r="L15" s="43">
+      <c r="L15" s="40">
         <v>1.1</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="2:12">
-      <c r="B16" s="46"/>
-      <c r="C16" s="19" t="s">
+      <c r="B16" s="38"/>
+      <c r="C16" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="H16" s="19">
-        <v>1</v>
-      </c>
-      <c r="I16" s="47" t="s">
+      <c r="H16" s="24">
+        <v>1</v>
+      </c>
+      <c r="I16" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="24">
         <v>0.94</v>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="24">
         <v>0.94</v>
       </c>
-      <c r="L16" s="48">
+      <c r="L16" s="47">
         <v>0.94</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="2:12">
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="24">
+      <c r="B17" s="29"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="31">
         <f t="shared" ref="H17:L17" si="0">SUM(H5:H16)</f>
         <v>12</v>
       </c>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24">
+      <c r="I17" s="31"/>
+      <c r="J17" s="31">
         <f>SUM(J5:J16)</f>
         <v>24.38</v>
       </c>
-      <c r="K17" s="24">
+      <c r="K17" s="31">
         <f t="shared" si="0"/>
         <v>24.38</v>
       </c>
-      <c r="L17" s="36">
+      <c r="L17" s="32">
         <f t="shared" si="0"/>
         <v>24.38</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="30" customHeight="1" spans="2:12">
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="37"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="35"/>
     </row>
     <row r="19" spans="2:12">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4280,7 +4290,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B3:L19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="20.625" style="4" customWidth="1"/>
@@ -4305,40 +4315,40 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="29"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="30" customHeight="1" spans="2:12">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="L4" s="31" t="s">
+      <c r="L4" s="15" t="s">
         <v>111</v>
       </c>
     </row>
@@ -4346,188 +4356,188 @@
       <c r="B5" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="16">
-        <v>1</v>
-      </c>
-      <c r="I5" s="42" t="s">
+      <c r="H5" s="19">
+        <v>1</v>
+      </c>
+      <c r="I5" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="19">
         <v>0.52</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="19">
         <v>0.52</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="40">
         <v>0.52</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="2:12">
       <c r="B6" s="38"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="15" t="s">
+      <c r="C6" s="23"/>
+      <c r="D6" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H6" s="16">
-        <v>1</v>
-      </c>
-      <c r="I6" s="42" t="s">
+      <c r="H6" s="19">
+        <v>1</v>
+      </c>
+      <c r="I6" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="19">
         <v>0.92</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="19">
         <v>0.92</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="40">
         <v>0.92</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="2:12">
       <c r="B7" s="38"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="15" t="s">
+      <c r="C7" s="23"/>
+      <c r="D7" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H7" s="16">
-        <v>1</v>
-      </c>
-      <c r="I7" s="42" t="s">
+      <c r="H7" s="19">
+        <v>1</v>
+      </c>
+      <c r="I7" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="19">
         <v>0.12</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="19">
         <v>0.12</v>
       </c>
-      <c r="L7" s="43">
+      <c r="L7" s="40">
         <v>0.12</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="2:12">
       <c r="B8" s="38"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="15" t="s">
+      <c r="C8" s="23"/>
+      <c r="D8" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="16">
-        <v>1</v>
-      </c>
-      <c r="I8" s="42" t="s">
+      <c r="H8" s="19">
+        <v>1</v>
+      </c>
+      <c r="I8" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="19">
         <v>2.2</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="19">
         <v>2.2</v>
       </c>
-      <c r="L8" s="43">
+      <c r="L8" s="40">
         <v>2.2</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:12">
       <c r="B9" s="38"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="15" t="s">
+      <c r="C9" s="23"/>
+      <c r="D9" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H9" s="16">
-        <v>1</v>
-      </c>
-      <c r="I9" s="42" t="s">
+      <c r="H9" s="19">
+        <v>1</v>
+      </c>
+      <c r="I9" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="19">
         <v>7.1</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="19">
         <v>7.1</v>
       </c>
-      <c r="L9" s="43">
+      <c r="L9" s="40">
         <v>7.1</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="2:12">
       <c r="B10" s="38"/>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="39">
+      <c r="H10" s="41">
         <v>1</v>
       </c>
       <c r="I10" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="39">
+      <c r="J10" s="41">
         <v>1.14</v>
       </c>
-      <c r="K10" s="39">
+      <c r="K10" s="41">
         <v>1.14</v>
       </c>
       <c r="L10" s="45">
@@ -4536,64 +4546,64 @@
     </row>
     <row r="11" ht="30" customHeight="1" spans="2:12">
       <c r="B11" s="38"/>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="G11" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="16">
-        <v>1</v>
-      </c>
-      <c r="I11" s="42" t="s">
+      <c r="H11" s="19">
+        <v>1</v>
+      </c>
+      <c r="I11" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="19">
         <v>0.92</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="19">
         <v>0.92</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="40">
         <v>0.92</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="2:12">
       <c r="B12" s="38"/>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="F12" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="G12" s="41" t="s">
+      <c r="G12" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H12" s="41">
         <v>1</v>
       </c>
       <c r="I12" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="J12" s="39">
+      <c r="J12" s="41">
         <v>0.12</v>
       </c>
-      <c r="K12" s="39">
+      <c r="K12" s="41">
         <v>0.12</v>
       </c>
       <c r="L12" s="45">
@@ -4602,64 +4612,64 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="2:12">
       <c r="B13" s="38"/>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H13" s="16">
-        <v>1</v>
-      </c>
-      <c r="I13" s="42" t="s">
+      <c r="H13" s="19">
+        <v>1</v>
+      </c>
+      <c r="I13" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="19">
         <v>2.2</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="19">
         <v>2.2</v>
       </c>
-      <c r="L13" s="43">
+      <c r="L13" s="40">
         <v>2.2</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="2:12">
       <c r="B14" s="38"/>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="G14" s="41" t="s">
+      <c r="G14" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="39">
+      <c r="H14" s="41">
         <v>1</v>
       </c>
       <c r="I14" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="J14" s="39">
+      <c r="J14" s="41">
         <v>7.1</v>
       </c>
-      <c r="K14" s="39">
+      <c r="K14" s="41">
         <v>7.1</v>
       </c>
       <c r="L14" s="45">
@@ -4668,64 +4678,64 @@
     </row>
     <row r="15" ht="30" customHeight="1" spans="2:12">
       <c r="B15" s="38"/>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="16">
-        <v>1</v>
-      </c>
-      <c r="I15" s="42" t="s">
+      <c r="H15" s="19">
+        <v>1</v>
+      </c>
+      <c r="I15" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="19">
         <v>1.1</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="19">
         <v>1.1</v>
       </c>
-      <c r="L15" s="43">
+      <c r="L15" s="40">
         <v>1.1</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="2:12">
       <c r="B16" s="38"/>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="G16" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="H16" s="39">
+      <c r="H16" s="41">
         <v>1</v>
       </c>
       <c r="I16" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="J16" s="39">
+      <c r="J16" s="41">
         <v>0.94</v>
       </c>
-      <c r="K16" s="39">
+      <c r="K16" s="41">
         <v>0.94</v>
       </c>
       <c r="L16" s="45">
@@ -4734,56 +4744,56 @@
     </row>
     <row r="17" ht="30" customHeight="1" spans="2:12">
       <c r="B17" s="38"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="24">
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="31">
         <f t="shared" ref="H17:L17" si="0">SUM(H5:H16)</f>
         <v>12</v>
       </c>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24">
+      <c r="I17" s="31"/>
+      <c r="J17" s="31">
         <f>SUM(J5:J16)</f>
         <v>24.38</v>
       </c>
-      <c r="K17" s="24">
+      <c r="K17" s="31">
         <f t="shared" si="0"/>
         <v>24.38</v>
       </c>
-      <c r="L17" s="36">
+      <c r="L17" s="32">
         <f t="shared" si="0"/>
         <v>24.38</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="30" customHeight="1" spans="2:12">
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="37"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="35"/>
     </row>
     <row r="19" spans="2:12">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4803,7 +4813,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B3:M20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="3" width="15.625" style="4" customWidth="1"/>
@@ -4828,539 +4838,539 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="29"/>
+      <c r="M3" s="8"/>
     </row>
     <row r="4" customFormat="1" ht="30" customHeight="1" spans="2:13">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="30"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="12"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="35" customHeight="1" spans="2:13">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="M5" s="31" t="s">
+      <c r="M5" s="15" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="2:13">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H6" s="16">
-        <v>1</v>
-      </c>
-      <c r="I6" s="16">
+      <c r="H6" s="19">
+        <v>1</v>
+      </c>
+      <c r="I6" s="19">
         <v>0.52</v>
       </c>
-      <c r="J6" s="32" t="s">
+      <c r="J6" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="K6" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="L6" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="M6" s="33" t="s">
+      <c r="M6" s="22" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="2:13">
-      <c r="B7" s="13"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="15" t="s">
+      <c r="B7" s="16"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H7" s="16">
-        <v>1</v>
-      </c>
-      <c r="I7" s="16">
+      <c r="H7" s="19">
+        <v>1</v>
+      </c>
+      <c r="I7" s="19">
         <v>0.92</v>
       </c>
-      <c r="J7" s="32" t="s">
+      <c r="J7" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="K7" s="32" t="s">
+      <c r="K7" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="L7" s="32" t="s">
+      <c r="L7" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="M7" s="33" t="s">
+      <c r="M7" s="22" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="2:13">
-      <c r="B8" s="13"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="15" t="s">
+      <c r="B8" s="16"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="16">
-        <v>1</v>
-      </c>
-      <c r="I8" s="16">
+      <c r="H8" s="19">
+        <v>1</v>
+      </c>
+      <c r="I8" s="19">
         <v>0.12</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="K8" s="32" t="s">
+      <c r="K8" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="L8" s="32" t="s">
+      <c r="L8" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="M8" s="33" t="s">
+      <c r="M8" s="22" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="2:13">
-      <c r="B9" s="13"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="15" t="s">
+      <c r="B9" s="16"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H9" s="16">
-        <v>1</v>
-      </c>
-      <c r="I9" s="16">
+      <c r="H9" s="19">
+        <v>1</v>
+      </c>
+      <c r="I9" s="19">
         <v>2.2</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="K9" s="32" t="s">
+      <c r="K9" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="L9" s="32" t="s">
+      <c r="L9" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="M9" s="33" t="s">
+      <c r="M9" s="22" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="2:13">
-      <c r="B10" s="13"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="15" t="s">
+      <c r="B10" s="16"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="16">
-        <v>1</v>
-      </c>
-      <c r="I10" s="16">
+      <c r="H10" s="19">
+        <v>1</v>
+      </c>
+      <c r="I10" s="19">
         <v>7.1</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="K10" s="32" t="s">
+      <c r="K10" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="L10" s="32" t="s">
+      <c r="L10" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="M10" s="33" t="s">
+      <c r="M10" s="22" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="2:13">
-      <c r="B11" s="13"/>
-      <c r="C11" s="19" t="s">
+      <c r="B11" s="16"/>
+      <c r="C11" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="19">
-        <v>1</v>
-      </c>
-      <c r="I11" s="19">
+      <c r="H11" s="24">
+        <v>1</v>
+      </c>
+      <c r="I11" s="24">
         <v>1.14</v>
       </c>
-      <c r="J11" s="34" t="s">
+      <c r="J11" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="K11" s="34" t="s">
+      <c r="K11" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="L11" s="34" t="s">
+      <c r="L11" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="M11" s="35" t="s">
+      <c r="M11" s="28" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="2:13">
-      <c r="B12" s="13"/>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="16"/>
+      <c r="C12" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H12" s="16">
-        <v>1</v>
-      </c>
-      <c r="I12" s="16">
+      <c r="H12" s="19">
+        <v>1</v>
+      </c>
+      <c r="I12" s="19">
         <v>0.92</v>
       </c>
-      <c r="J12" s="32" t="s">
+      <c r="J12" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="K12" s="32" t="s">
+      <c r="K12" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="L12" s="32" t="s">
+      <c r="L12" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="M12" s="33" t="s">
+      <c r="M12" s="22" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="2:13">
-      <c r="B13" s="13"/>
-      <c r="C13" s="19" t="s">
+      <c r="B13" s="16"/>
+      <c r="C13" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="H13" s="19">
-        <v>1</v>
-      </c>
-      <c r="I13" s="19">
+      <c r="H13" s="24">
+        <v>1</v>
+      </c>
+      <c r="I13" s="24">
         <v>0.12</v>
       </c>
-      <c r="J13" s="34" t="s">
+      <c r="J13" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="K13" s="34" t="s">
+      <c r="K13" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="L13" s="34" t="s">
+      <c r="L13" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="M13" s="35" t="s">
+      <c r="M13" s="28" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="2:13">
-      <c r="B14" s="13"/>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="16"/>
+      <c r="C14" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="16">
-        <v>1</v>
-      </c>
-      <c r="I14" s="16">
+      <c r="H14" s="19">
+        <v>1</v>
+      </c>
+      <c r="I14" s="19">
         <v>2.2</v>
       </c>
-      <c r="J14" s="32" t="s">
+      <c r="J14" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="K14" s="32" t="s">
+      <c r="K14" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="L14" s="32" t="s">
+      <c r="L14" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="M14" s="33" t="s">
+      <c r="M14" s="22" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="2:13">
-      <c r="B15" s="13"/>
-      <c r="C15" s="19" t="s">
+      <c r="B15" s="16"/>
+      <c r="C15" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="G15" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="19">
-        <v>1</v>
-      </c>
-      <c r="I15" s="19">
+      <c r="H15" s="24">
+        <v>1</v>
+      </c>
+      <c r="I15" s="24">
         <v>7.1</v>
       </c>
-      <c r="J15" s="34" t="s">
+      <c r="J15" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="K15" s="34" t="s">
+      <c r="K15" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="L15" s="34" t="s">
+      <c r="L15" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="M15" s="35" t="s">
+      <c r="M15" s="28" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="2:13">
-      <c r="B16" s="13"/>
-      <c r="C16" s="16" t="s">
+      <c r="B16" s="16"/>
+      <c r="C16" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H16" s="16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="16">
+      <c r="H16" s="19">
+        <v>1</v>
+      </c>
+      <c r="I16" s="19">
         <v>1.1</v>
       </c>
-      <c r="J16" s="32" t="s">
+      <c r="J16" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="K16" s="32" t="s">
+      <c r="K16" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="L16" s="32" t="s">
+      <c r="L16" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="M16" s="33" t="s">
+      <c r="M16" s="22" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="2:13">
-      <c r="B17" s="13"/>
-      <c r="C17" s="19" t="s">
+      <c r="B17" s="16"/>
+      <c r="C17" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="H17" s="19">
-        <v>1</v>
-      </c>
-      <c r="I17" s="19">
+      <c r="H17" s="24">
+        <v>1</v>
+      </c>
+      <c r="I17" s="24">
         <v>0.94</v>
       </c>
-      <c r="J17" s="34" t="s">
+      <c r="J17" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="K17" s="34" t="s">
+      <c r="K17" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="L17" s="34" t="s">
+      <c r="L17" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="M17" s="35" t="s">
+      <c r="M17" s="28" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="2:13">
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="24">
+      <c r="B18" s="29"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="31">
         <f t="shared" ref="H18:L18" si="0">SUM(H6:H17)</f>
         <v>12</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="31">
         <f t="shared" si="0"/>
         <v>24.38</v>
       </c>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="36"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="32"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="30" customHeight="1" spans="2:13">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="37"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="35"/>
     </row>
     <row r="20" spans="2:13">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
